--- a/PD_Guide_Database.xlsx
+++ b/PD_Guide_Database.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="Recf7296a22e148f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="Rb6164e3b50dd4962"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="Rcf6cfbb734e84b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="R26f516866cdf4b6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="Rcb3a229c07534ae2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="Rb3913aaeb1a14e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R6d2031311c054898"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="R14bb7df323fd4ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thinkpad" sheetId="1" r:id="Rd48a7a45d26748cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ideapad" sheetId="2" r:id="Ra347797b94404dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desktop" sheetId="3" r:id="R1491c64d8518456c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiny" sheetId="4" r:id="Re8c9a62149a246e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIO" sheetId="5" r:id="R3b924548786c42b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown_Master" sheetId="6" r:id="R7fd3b6f480b74c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related_Guide_Master" sheetId="7" r:id="R1ec8df23a1c64c64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" r:id="Rb8fea38f5fde47fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2912,7 +2912,7 @@
         <x:v>Abnormal Line</x:v>
       </x:c>
       <x:c r="C108" s="61" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D108" s="61" t="str">
         <x:v>DD002</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>Flickering</x:v>
       </x:c>
       <x:c r="C115" s="61" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D115" s="61" t="str">
         <x:v>DD002</x:v>
@@ -3248,7 +3248,7 @@
         <x:v>Dim</x:v>
       </x:c>
       <x:c r="C124" s="61" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D124" s="61" t="str">
         <x:v>DD002</x:v>
@@ -3416,7 +3416,7 @@
         <x:v>Black Screen</x:v>
       </x:c>
       <x:c r="C132" s="61" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D132" s="61" t="str">
         <x:v>DD002</x:v>
@@ -3563,7 +3563,7 @@
         <x:v>Color Bias</x:v>
       </x:c>
       <x:c r="C139" s="63" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D139" s="63" t="str">
         <x:v>DD002</x:v>
@@ -3710,7 +3710,7 @@
         <x:v>Garbage</x:v>
       </x:c>
       <x:c r="C146" s="61" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D146" s="61" t="str">
         <x:v>DD002</x:v>
@@ -10713,7 +10713,7 @@
         <x:v>Monitor Flickering</x:v>
       </x:c>
       <x:c r="C478" s="61" t="str">
-        <x:v>Swap HDMI / DisplayPort Cable</x:v>
+        <x:v>swap HDMI cable</x:v>
       </x:c>
       <x:c r="D478" s="61" t="str">
         <x:v>DD002</x:v>
@@ -10860,7 +10860,7 @@
         <x:v>No Signal / HDMI / DisplayPort</x:v>
       </x:c>
       <x:c r="C485" s="61" t="str">
-        <x:v>Swap HDMI / DisplayPort Cable</x:v>
+        <x:v>swap HDMI cable</x:v>
       </x:c>
       <x:c r="D485" s="61" t="str">
         <x:v>DD002</x:v>
@@ -14628,7 +14628,7 @@
         <x:v>Abnormal Line</x:v>
       </x:c>
       <x:c r="C103" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D103" s="52" t="str">
         <x:v>DD002</x:v>
@@ -14943,7 +14943,7 @@
         <x:v>Dim</x:v>
       </x:c>
       <x:c r="C118" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D118" s="52" t="str">
         <x:v>DD002</x:v>
@@ -15279,7 +15279,7 @@
         <x:v>Color Bias</x:v>
       </x:c>
       <x:c r="C134" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D134" s="52" t="str">
         <x:v>DD002</x:v>
@@ -24371,7 +24371,7 @@
         <x:v>Power on No Display</x:v>
       </x:c>
       <x:c r="C16" s="52" t="str">
-        <x:v>Swap HDMI / DisplayPort Cable</x:v>
+        <x:v>swap HDMI cable</x:v>
       </x:c>
       <x:c r="D16" s="52" t="str">
         <x:v>DD002</x:v>
@@ -26245,7 +26245,7 @@
         <x:v>Display Abnormal Line</x:v>
       </x:c>
       <x:c r="C103" s="52" t="str">
-        <x:v>Swap HDMI / DisplayPort Cable</x:v>
+        <x:v>swap HDMI cable</x:v>
       </x:c>
       <x:c r="D103" s="52" t="str">
         <x:v>DD002</x:v>
@@ -26497,16 +26497,16 @@
         <x:v>Flickering</x:v>
       </x:c>
       <x:c r="C115" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D115" s="52" t="str">
         <x:v>DD002</x:v>
       </x:c>
       <x:c r="E115" s="52" t="str">
-        <x:v>ตรวจสอบหน้า Bios หรือ Diagnostics พบอาการลักษณะเดียวกันหรือไม่</x:v>
+        <x:v>ตรวจสอบหน้า BIOS ว่าพบอาการลักษณะเดียวกันหรือไม่</x:v>
       </x:c>
       <x:c r="F115" s="52" t="str">
-        <x:v>Check whether the same issue occurs in BIOS or Lenovo Diagnostics.</x:v>
+        <x:v>Check whether the same issue occurs in BIOS.</x:v>
       </x:c>
       <x:c r="G115" s="52"/>
     </x:row>
@@ -26518,16 +26518,16 @@
         <x:v>Flickering</x:v>
       </x:c>
       <x:c r="C116" s="52" t="str">
-        <x:v>Move LCD Lid</x:v>
+        <x:v>swap HDMI cable</x:v>
       </x:c>
       <x:c r="D116" s="52" t="str">
         <x:v>DD002</x:v>
       </x:c>
       <x:c r="E116" s="52" t="str">
-        <x:v>ทดสอบขยับฝาจอ LCD ช้า ๆ และตรวจสอบว่าภาพมีอาการผิดปกติหรือไม่</x:v>
+        <x:v>ทดสอบสลับสาย HDMI เส้นอื่น</x:v>
       </x:c>
       <x:c r="F116" s="52" t="str">
-        <x:v>Slowly move the LCD lid and check whether the image becomes abnormal.</x:v>
+        <x:v>Test with another HDMI cable.</x:v>
       </x:c>
       <x:c r="G116" s="52"/>
     </x:row>
@@ -26539,16 +26539,16 @@
         <x:v>Flickering</x:v>
       </x:c>
       <x:c r="C117" s="52" t="str">
-        <x:v>External Monitor Test</x:v>
+        <x:v>Monitor Test on Other Machine</x:v>
       </x:c>
       <x:c r="D117" s="52" t="str">
         <x:v>DD002</x:v>
       </x:c>
       <x:c r="E117" s="52" t="str">
-        <x:v>ทดสอบต่อจอนอก และตรวจสอบว่าใช้งานได้ปกติหรือไม่</x:v>
+        <x:v>ทดสอบจอภาพกับเครื่องอื่น</x:v>
       </x:c>
       <x:c r="F117" s="52" t="str">
-        <x:v>Connect an external monitor and check whether it works normally.</x:v>
+        <x:v>Test the Monitor with another machine.</x:v>
       </x:c>
       <x:c r="G117" s="52"/>
     </x:row>
@@ -26560,16 +26560,16 @@
         <x:v>Flickering</x:v>
       </x:c>
       <x:c r="C118" s="52" t="str">
-        <x:v>Lenovo Vantage Update</x:v>
+        <x:v>Swap Monitor</x:v>
       </x:c>
       <x:c r="D118" s="52" t="str">
-        <x:v>DD009</x:v>
+        <x:v>DD002</x:v>
       </x:c>
       <x:c r="E118" s="52" t="str">
-        <x:v>ทดสอบอัปเดตไดรเวอร์ทั้งหมดผ่านโปรแกรม Lenovo Vantage</x:v>
+        <x:v>ทดสอบสลับ Monitor ตัวอื่น</x:v>
       </x:c>
       <x:c r="F118" s="52" t="str">
-        <x:v>Open Lenovo Vantage and install all available driver updates.</x:v>
+        <x:v>Test with another monitor.</x:v>
       </x:c>
       <x:c r="G118" s="52"/>
     </x:row>
@@ -35681,7 +35681,7 @@
         <x:v>Flickering</x:v>
       </x:c>
       <x:c r="C110" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D110" s="52" t="str">
         <x:v>DD002</x:v>
@@ -44611,7 +44611,7 @@
         <x:v>Abnormal Line</x:v>
       </x:c>
       <x:c r="C87" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D87" s="52" t="str">
         <x:v>DD002</x:v>
@@ -44926,7 +44926,7 @@
         <x:v>Dim</x:v>
       </x:c>
       <x:c r="C102" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D102" s="52" t="str">
         <x:v>DD002</x:v>
@@ -45262,7 +45262,7 @@
         <x:v>Color Bias</x:v>
       </x:c>
       <x:c r="C118" s="52" t="str">
-        <x:v>Check BIOS / Diagnostics</x:v>
+        <x:v>Check BIOS</x:v>
       </x:c>
       <x:c r="D118" s="52" t="str">
         <x:v>DD002</x:v>
@@ -53010,7 +53010,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>PD Guide Toolkit v5.2.6 adds selective inline Related Guide ⓘ popups in SYMPTOMS.</x:v>
+        <x:v>PD Guide Toolkit v5.2.9: corrected Desktop &gt; Monitor &gt; Flickering to use desktop/external-monitor troubleshooting instead of notebook display steps.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
